--- a/productos_sede_ronaldo.xlsx
+++ b/productos_sede_ronaldo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcamp\Desktop\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD92D3A-F05A-44DD-BEF3-6CD8A585E967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D296F7-1B30-48F4-A0B3-6D66254402EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Producto</t>
   </si>
@@ -78,7 +78,10 @@
     <t>Holder tipo araña</t>
   </si>
   <si>
-    <t>Precios</t>
+    <t>P. compra</t>
+  </si>
+  <si>
+    <t>P. venta</t>
   </si>
 </sst>
 </file>
@@ -86,7 +89,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$S/-280A]\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$S/-280A]\ #,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -113,7 +116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -136,16 +139,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,14 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.21875" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="2" max="3" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,181 +461,227 @@
       <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
+        <v>10.5</v>
+      </c>
+      <c r="D3" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2">
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2">
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C22" s="2"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/productos_sede_ronaldo.xlsx
+++ b/productos_sede_ronaldo.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcamp\Desktop\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D296F7-1B30-48F4-A0B3-6D66254402EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A98031-E4FE-4816-8E37-2BF6B0590F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Producto</t>
   </si>
@@ -82,6 +91,18 @@
   </si>
   <si>
     <t>P. venta</t>
+  </si>
+  <si>
+    <t>P. vendido</t>
+  </si>
+  <si>
+    <t>P. registrar</t>
+  </si>
+  <si>
+    <t>C. inicial</t>
+  </si>
+  <si>
+    <t>C. Actual</t>
   </si>
 </sst>
 </file>
@@ -444,43 +465,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.21875" customWidth="1"/>
-    <col min="2" max="3" width="11.77734375" customWidth="1"/>
+    <col min="2" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
+        <f>B2-G2</f>
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
         <v>23</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <f>((F2*G2)-(D2*G2))/2+(D2*G2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -488,13 +530,21 @@
         <v>2</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C3:C30" si="0">B3-G3</f>
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>10.5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <f t="shared" ref="H3:H26" si="1">((F3*G3)-(D3*G3))/2+(D3*G3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -502,13 +552,21 @@
         <v>1</v>
       </c>
       <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D4">
         <v>31</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -516,13 +574,21 @@
         <v>2</v>
       </c>
       <c r="C5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D5">
         <v>5.5</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -530,13 +596,21 @@
         <v>2</v>
       </c>
       <c r="C6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>26</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -544,13 +618,21 @@
         <v>2</v>
       </c>
       <c r="C7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D7">
         <v>13</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -558,13 +640,21 @@
         <v>2</v>
       </c>
       <c r="C8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D8">
         <v>9</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -572,13 +662,21 @@
         <v>1</v>
       </c>
       <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D9">
         <v>9</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -586,13 +684,27 @@
         <v>2</v>
       </c>
       <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D10">
         <v>10</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>29</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -600,13 +712,21 @@
         <v>2</v>
       </c>
       <c r="C11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D11">
         <v>48</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>79</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -614,13 +734,21 @@
         <v>2</v>
       </c>
       <c r="C12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D12">
         <v>29</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>59</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -628,13 +756,21 @@
         <v>2</v>
       </c>
       <c r="C13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D13">
         <v>48</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>105</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -642,13 +778,21 @@
         <v>1</v>
       </c>
       <c r="C14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D14">
         <v>50</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>119</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -656,32 +800,160 @@
         <v>2</v>
       </c>
       <c r="C15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D15">
         <v>8</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D22" s="2"/>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/productos_sede_ronaldo.xlsx
+++ b/productos_sede_ronaldo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcamp\Desktop\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A98031-E4FE-4816-8E37-2BF6B0590F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8DD22B-6022-4A88-B3C3-66B99099A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,11 +681,11 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -797,11 +797,11 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>8</v>

--- a/productos_sede_ronaldo.xlsx
+++ b/productos_sede_ronaldo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcamp\Desktop\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8DD22B-6022-4A88-B3C3-66B99099A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E81114-0767-435C-BC1F-9C582EA73D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,11 +731,11 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>29</v>
